--- a/WorkBot/refactor-experimental/data/orders/A.L. George/A.L. George_Collegetown_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/A.L. George/A.L. George_Collegetown_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,133 +446,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>77220</t>
+          <t>75155</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Guayaki Yerba Mate - Enlighten Mint</t>
+          <t>Essentia Water</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.00</t>
+          <t>49.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>75155</t>
+          <t>74602</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Essentia Water</t>
+          <t>Evian 1L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>69.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>75112</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Evian 1L</t>
+          <t>Fiji Water 1L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.00</t>
+          <t>49.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>75112</t>
+          <t>77802</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fiji Water 1L</t>
+          <t>Ithaca Soda - Ginger Beer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>77802</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ithaca Soda - Ginger Beer</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>23.95</t>
         </is>
